--- a/docs/03_test/部署一覧_テストケース.xlsx
+++ b/docs/03_test/部署一覧_テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D477128-2DDC-47E7-85C3-DC4122DD33C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30D90BB3-B461-4629-95E4-EBDD5B921553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9C3BC887-3E63-44CA-B9AA-47FE237A9488}"/>
   </bookViews>
@@ -114,7 +114,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +132,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -207,12 +216,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -231,8 +243,12 @@
     <xf numFmtId="56" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -662,7 +678,7 @@
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -679,7 +695,7 @@
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -691,6 +707,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="D3" location="Sheet2!A1" display="部署一覧画面に遷移する" xr:uid="{748C5650-7EF8-4281-858C-8DA44D96FEE6}"/>
+    <hyperlink ref="D4" location="Sheet2!A1" display="DBにある部署がすべて表示される" xr:uid="{11624210-061B-454D-B074-E93A0A58D1AE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/03_test/部署一覧_テストケース.xlsx
+++ b/docs/03_test/部署一覧_テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30D90BB3-B461-4629-95E4-EBDD5B921553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2AEB8D-07D3-4DFD-B5C8-BEEE81DCB0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9C3BC887-3E63-44CA-B9AA-47FE237A9488}"/>
   </bookViews>
@@ -103,8 +103,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>部署の一覧が表示される</t>
-    <rPh sb="0" eb="2">
+    <t>一覧画面に部署の一覧が表示される</t>
+    <rPh sb="0" eb="4">
+      <t>イチランガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>ブショ</t>
     </rPh>
     <phoneticPr fontId="2"/>
